--- a/student_import_template.xlsx
+++ b/student_import_template.xlsx
@@ -397,7 +397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="33.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="30.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -428,9 +442,12 @@
         <v>Semester</v>
       </c>
       <c r="J1" t="str">
+        <v>University Registration Number</v>
+      </c>
+      <c r="K1" t="str">
         <v>Roll Number</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Industrial Registration Number</v>
       </c>
     </row>
@@ -463,9 +480,12 @@
         <v>Semester 5</v>
       </c>
       <c r="J2" t="str">
+        <v>REG-2026-1001</v>
+      </c>
+      <c r="K2" t="str">
         <v>ROLL-2026-001</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>IM-23-8801</v>
       </c>
     </row>
@@ -498,9 +518,12 @@
         <v>Semester 5</v>
       </c>
       <c r="J3" t="str">
+        <v>REG-2026-1002</v>
+      </c>
+      <c r="K3" t="str">
         <v>ROLL-2026-002</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>IM-23-8802</v>
       </c>
     </row>
@@ -533,15 +556,18 @@
         <v>Semester 5</v>
       </c>
       <c r="J4" t="str">
+        <v>REG-2026-1003</v>
+      </c>
+      <c r="K4" t="str">
         <v>ROLL-2026-003</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>IM-23-8803</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>